--- a/metainfer/tasks/dcu_kernel_auto_opt/reports/dkao_optimized_operators_bestvariant.xlsx
+++ b/metainfer/tasks/dcu_kernel_auto_opt/reports/dkao_optimized_operators_bestvariant.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'汇总-最优variant'!$A$1:$T$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'按模型×TP汇总'!$A$1:$J$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'汇总-最优variant'!$A$1:$U$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'按模型×TP汇总'!$A$1:$K$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -87,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -126,9 +126,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -500,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T34"/>
+  <dimension ref="A1:U38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -523,6 +521,7 @@
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -626,6 +625,11 @@
           <t>任务完成时间</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>验收状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -706,6 +710,11 @@
           <t>2026-08-26 14:59</t>
         </is>
       </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -786,6 +795,11 @@
           <t>2026-08-26 14:59</t>
         </is>
       </c>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -866,6 +880,11 @@
           <t>2026-08-26 14:59</t>
         </is>
       </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -946,6 +965,11 @@
           <t>2026-08-26 14:59</t>
         </is>
       </c>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1026,6 +1050,11 @@
           <t>2026-08-22 05:44</t>
         </is>
       </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1106,6 +1135,11 @@
           <t>2026-08-22 05:44</t>
         </is>
       </c>
+      <c r="U7" s="7" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1186,6 +1220,11 @@
           <t>2026-08-22 05:44</t>
         </is>
       </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -1266,6 +1305,11 @@
           <t>2026-08-22 05:44</t>
         </is>
       </c>
+      <c r="U9" s="7" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1346,6 +1390,11 @@
           <t>2026-08-27 07:23</t>
         </is>
       </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -1426,6 +1475,11 @@
           <t>2026-08-27 07:23</t>
         </is>
       </c>
+      <c r="U11" s="7" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1506,6 +1560,11 @@
           <t>2026-08-27 07:23</t>
         </is>
       </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -1586,21 +1645,26 @@
           <t>2026-08-27 07:23</t>
         </is>
       </c>
+      <c r="U13" s="7" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>minimax-dsh-tp8-m16-1-78402260</t>
+          <t>hy3-dsh-tp8-m16-9-8-0161e718</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MiniMax-M3 (gfx928 INT8 W8A8)</t>
+          <t>Hy3 (gfx928 INT8 W8A8)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>minimax-dsh-TP8-m16-1</t>
+          <t>hy3-dsh-TP8-M16-9.8</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1618,7 +1682,7 @@
         <v>1280</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>6144</v>
+        <v>4096</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -1626,61 +1690,54 @@
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>110.478</v>
+        <v>74.782</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>33.2017</v>
+        <v>19.2968</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>worker_0 accepted/minimax_tp8_qkv_proj_m16/kernel.hip</t>
+          <t>worker_0 accepted/&lt;shape&gt; (n=30 samples)</t>
         </is>
       </c>
       <c r="M14" s="4" t="n">
-        <v>33.1958</v>
+        <v>19.2968</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>33.3286</v>
+        <v>19.3232</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>3.3281</v>
+        <v>3.8754</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>232.8073</v>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
+        <v>287.536</v>
+      </c>
+      <c r="Q14" s="6" t="inlineStr"/>
+      <c r="R14" s="6" t="inlineStr"/>
       <c r="S14" s="5" t="n">
-        <v>7.581</v>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28 17:17</t>
+        <v>8.6943</v>
+      </c>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>仅worker验收(未过最终验收)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>minimax-dsh-tp8-m16-1-78402260</t>
+          <t>hy3-dsh-tp8-m16-9-8-0161e718</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>MiniMax-M3 (gfx928 INT8 W8A8)</t>
+          <t>Hy3 (gfx928 INT8 W8A8)</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>minimax-dsh-TP8-m16-1</t>
+          <t>hy3-dsh-TP8-M16-9.8</t>
         </is>
       </c>
       <c r="D15" s="8" t="n">
@@ -1688,17 +1745,17 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>qkv_proj_and_indexer_qk</t>
+          <t>o_proj</t>
         </is>
       </c>
       <c r="F15" s="8" t="n">
         <v>16</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>1536</v>
+        <v>4096</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>6144</v>
+        <v>1024</v>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
@@ -1706,61 +1763,54 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>111.486</v>
+        <v>32.137</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>39.7272</v>
+        <v>11.044</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>worker_1 accepted/minimax_tp8_qkv_proj_and_indexer_qk_m16/kernel.hip</t>
+          <t>worker_1 accepted/&lt;shape&gt; (n=30 samples)</t>
         </is>
       </c>
       <c r="M15" s="9" t="n">
-        <v>39.7375</v>
+        <v>11.044</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>39.8535</v>
+        <v>11.1632</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>2.8056</v>
+        <v>2.9099</v>
       </c>
       <c r="P15" s="10" t="n">
-        <v>180.5563</v>
-      </c>
-      <c r="Q15" s="11" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="R15" s="11" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
+        <v>190.9909</v>
+      </c>
+      <c r="Q15" s="11" t="inlineStr"/>
+      <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="10" t="n">
-        <v>7.5996</v>
-      </c>
-      <c r="T15" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-28 17:17</t>
+        <v>12.153</v>
+      </c>
+      <c r="T15" s="7" t="inlineStr"/>
+      <c r="U15" s="7" t="inlineStr">
+        <is>
+          <t>仅worker验收(未过最终验收)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>minimax-dsh-tp8-m16-1-78402260</t>
+          <t>hy3-dsh-tp8-m16-9-8-0161e718</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>MiniMax-M3 (gfx928 INT8 W8A8)</t>
+          <t>Hy3 (gfx928 INT8 W8A8)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>minimax-dsh-TP8-m16-1</t>
+          <t>hy3-dsh-TP8-M16-9.8</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1768,17 +1818,17 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>o_proj</t>
+          <t>shared_gate_up_proj</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
         <v>16</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>6144</v>
+        <v>384</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1024</v>
+        <v>4096</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -1786,61 +1836,54 @@
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>38.655</v>
+        <v>66.527</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>11.3688</v>
+        <v>12.488</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>worker_2 accepted/minimax_tp8_o_proj_m16/kernel.hip</t>
+          <t>worker_2 accepted/&lt;shape&gt; (n=30 samples)</t>
         </is>
       </c>
       <c r="M16" s="4" t="n">
-        <v>11.773</v>
+        <v>12.488</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>12.421</v>
+        <v>12.5344</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.2834</v>
+        <v>5.3273</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>228.336</v>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
+        <v>432.7287</v>
+      </c>
+      <c r="Q16" s="6" t="inlineStr"/>
+      <c r="R16" s="6" t="inlineStr"/>
       <c r="S16" s="5" t="n">
-        <v>17.1007</v>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28 17:17</t>
+        <v>4.0304</v>
+      </c>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>仅worker验收(未过最终验收)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>minimax-dsh-tp8-m16-1-78402260</t>
+          <t>hy3-dsh-tp8-m16-9-8-0161e718</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>MiniMax-M3 (gfx928 INT8 W8A8)</t>
+          <t>Hy3 (gfx928 INT8 W8A8)</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>minimax-dsh-TP8-m16-1</t>
+          <t>hy3-dsh-TP8-M16-9.8</t>
         </is>
       </c>
       <c r="D17" s="8" t="n">
@@ -1848,17 +1891,17 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>shared_gate_up_proj</t>
+          <t>shared_down_proj</t>
         </is>
       </c>
       <c r="F17" s="8" t="n">
         <v>16</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>768</v>
+        <v>4096</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>6144</v>
+        <v>192</v>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
@@ -1866,44 +1909,37 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>104.527</v>
+        <v>17.312</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>17.1145</v>
+        <v>8.6708</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>worker_3 accepted/minimax_tp8_shared_gate_up_proj_m16/kernel.hip</t>
+          <t>worker_3 accepted/&lt;shape&gt; (n=30 samples)</t>
         </is>
       </c>
       <c r="M17" s="9" t="n">
-        <v>17.3195</v>
+        <v>8.6708</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>17.5011</v>
+        <v>9.144399999999999</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>6.0352</v>
+        <v>1.9966</v>
       </c>
       <c r="P17" s="10" t="n">
-        <v>503.5224</v>
-      </c>
-      <c r="Q17" s="11" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="R17" s="11" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
+        <v>99.658</v>
+      </c>
+      <c r="Q17" s="11" t="inlineStr"/>
+      <c r="R17" s="11" t="inlineStr"/>
       <c r="S17" s="10" t="n">
-        <v>8.7182</v>
-      </c>
-      <c r="T17" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-28 17:17</t>
+        <v>2.9024</v>
+      </c>
+      <c r="T17" s="7" t="inlineStr"/>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>仅worker验收(未过最终验收)</t>
         </is>
       </c>
     </row>
@@ -1928,45 +1964,45 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>shared_down_proj</t>
+          <t>qkv_proj</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
         <v>16</v>
       </c>
       <c r="G18" s="3" t="n">
+        <v>1280</v>
+      </c>
+      <c r="H18" s="3" t="n">
         <v>6144</v>
       </c>
-      <c r="H18" s="3" t="n">
-        <v>384</v>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>INT8 W8A8</t>
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>23.152</v>
+        <v>110.478</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>8.9528</v>
+        <v>33.2017</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>worker_3 accepted/minimax_tp8_shared_down_proj_m16/kernel.hip</t>
+          <t>worker_0 accepted/minimax_tp8_qkv_proj_m16/kernel.hip</t>
         </is>
       </c>
       <c r="M18" s="4" t="n">
-        <v>9.3414</v>
+        <v>33.1958</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>10.1758</v>
+        <v>33.3286</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.4784</v>
+        <v>3.3281</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>147.8421</v>
+        <v>232.8073</v>
       </c>
       <c r="Q18" s="6" t="inlineStr">
         <is>
@@ -1979,18 +2015,23 @@
         </is>
       </c>
       <c r="S18" s="5" t="n">
-        <v>8.082000000000001</v>
+        <v>7.581</v>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
           <t>2026-08-28 17:17</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>minimaxm3-dsh-tp4-m4096-1-0c2f84a9</t>
+          <t>minimax-dsh-tp8-m16-1-78402260</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -2000,22 +2041,22 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>minimaxM3-dsh_TP4_M4096-1</t>
+          <t>minimax-dsh-TP8-m16-1</t>
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>qkv_proj</t>
+          <t>qkv_proj_and_indexer_qk</t>
         </is>
       </c>
       <c r="F19" s="8" t="n">
-        <v>4096</v>
+        <v>16</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>2304</v>
+        <v>1536</v>
       </c>
       <c r="H19" s="8" t="n">
         <v>6144</v>
@@ -2026,27 +2067,27 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>31556.192</v>
+        <v>111.486</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>1559.9448</v>
+        <v>39.7272</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>worker_0 accepted/minimax_tp4_qkv_proj_m4096/kernel.hip</t>
+          <t>worker_1 accepted/minimax_tp8_qkv_proj_and_indexer_qk_m16/kernel.hip</t>
         </is>
       </c>
       <c r="M19" s="9" t="n">
-        <v>1561.9083</v>
+        <v>39.7375</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>1577.3059</v>
+        <v>39.8535</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>20.2036</v>
+        <v>2.8056</v>
       </c>
       <c r="P19" s="10" t="n">
-        <v>1920.3613</v>
+        <v>180.5563</v>
       </c>
       <c r="Q19" s="11" t="inlineStr">
         <is>
@@ -2059,18 +2100,23 @@
         </is>
       </c>
       <c r="S19" s="10" t="n">
-        <v>74.24509999999999</v>
+        <v>7.5996</v>
       </c>
       <c r="T19" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 18:45</t>
+          <t>2026-08-28 17:17</t>
+        </is>
+      </c>
+      <c r="U19" s="7" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>minimaxm3-dsh-tp4-m4096-1-0c2f84a9</t>
+          <t>minimax-dsh-tp8-m16-1-78402260</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -2080,25 +2126,25 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>minimaxM3-dsh_TP4_M4096-1</t>
+          <t>minimax-dsh-TP8-m16-1</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>qkv_proj_and_indexer_qk</t>
+          <t>o_proj</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>4096</v>
+        <v>16</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2560</v>
+        <v>6144</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>6144</v>
+        <v>1024</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
@@ -2106,27 +2152,27 @@
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>35918.768</v>
+        <v>38.655</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1081.6037</v>
+        <v>11.3688</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>worker_1 accepted/minimax_tp4_qkv_proj_and_indexer_qk_m4096/kernel.hip</t>
+          <t>worker_2 accepted/minimax_tp8_o_proj_m16/kernel.hip</t>
         </is>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1089.0154</v>
+        <v>11.773</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1102.6435</v>
+        <v>12.421</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>32.9828</v>
+        <v>3.2834</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>3198.2791</v>
+        <v>228.336</v>
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
@@ -2139,18 +2185,23 @@
         </is>
       </c>
       <c r="S20" s="5" t="n">
-        <v>118.317</v>
+        <v>17.1007</v>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23 18:45</t>
+          <t>2026-08-28 17:17</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>minimaxm3-dsh-tp4-m4096-1-0c2f84a9</t>
+          <t>minimax-dsh-tp8-m16-1-78402260</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -2160,53 +2211,53 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>minimaxM3-dsh_TP4_M4096-1</t>
+          <t>minimax-dsh-TP8-m16-1</t>
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>o_proj</t>
+          <t>shared_gate_up_proj</t>
         </is>
       </c>
       <c r="F21" s="8" t="n">
-        <v>4096</v>
+        <v>16</v>
       </c>
       <c r="G21" s="8" t="n">
+        <v>768</v>
+      </c>
+      <c r="H21" s="8" t="n">
         <v>6144</v>
       </c>
-      <c r="H21" s="8" t="n">
-        <v>2048</v>
-      </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
           <t>INT8 W8A8</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>29702.473</v>
+        <v>104.527</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>765.9098</v>
+        <v>17.1145</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>worker_2 accepted/minimax_tp4_o_proj_m4096/kernel.hip</t>
+          <t>worker_3 accepted/minimax_tp8_shared_gate_up_proj_m16/kernel.hip</t>
         </is>
       </c>
       <c r="M21" s="9" t="n">
-        <v>752.485</v>
+        <v>17.3195</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>753.6546</v>
+        <v>17.5011</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>39.4725</v>
+        <v>6.0352</v>
       </c>
       <c r="P21" s="10" t="n">
-        <v>3847.2513</v>
+        <v>503.5224</v>
       </c>
       <c r="Q21" s="11" t="inlineStr">
         <is>
@@ -2219,18 +2270,23 @@
         </is>
       </c>
       <c r="S21" s="10" t="n">
-        <v>136.9851</v>
+        <v>8.7182</v>
       </c>
       <c r="T21" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 18:45</t>
+          <t>2026-08-28 17:17</t>
+        </is>
+      </c>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>minimaxm3-dsh-tp4-m4096-1-0c2f84a9</t>
+          <t>minimax-dsh-tp8-m16-1-78402260</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2240,25 +2296,25 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>minimaxM3-dsh_TP4_M4096-1</t>
+          <t>minimax-dsh-TP8-m16-1</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>shared_gate_up_proj</t>
+          <t>shared_down_proj</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>4096</v>
+        <v>16</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1536</v>
+        <v>6144</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>6144</v>
+        <v>384</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
@@ -2266,27 +2322,27 @@
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>19776.488</v>
+        <v>23.152</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>986.5248</v>
+        <v>8.9528</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>worker_3 accepted/minimax_tp4_shared_gate_up_proj_m4096/kernel.hip</t>
+          <t>worker_3 accepted/minimax_tp8_shared_down_proj_m16/kernel.hip</t>
         </is>
       </c>
       <c r="M22" s="4" t="n">
-        <v>962.3475</v>
+        <v>9.3414</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>965.7874</v>
+        <v>10.1758</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>20.5503</v>
+        <v>2.4784</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>1955.0258</v>
+        <v>147.8421</v>
       </c>
       <c r="Q22" s="6" t="inlineStr">
         <is>
@@ -2299,11 +2355,16 @@
         </is>
       </c>
       <c r="S22" s="5" t="n">
-        <v>80.3342</v>
+        <v>8.082000000000001</v>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23 18:45</t>
+          <t>2026-08-28 17:17</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
         </is>
       </c>
     </row>
@@ -2328,45 +2389,45 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>shared_down_proj</t>
+          <t>qkv_proj</t>
         </is>
       </c>
       <c r="F23" s="8" t="n">
         <v>4096</v>
       </c>
       <c r="G23" s="8" t="n">
+        <v>2304</v>
+      </c>
+      <c r="H23" s="8" t="n">
         <v>6144</v>
       </c>
-      <c r="H23" s="8" t="n">
-        <v>768</v>
-      </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
           <t>INT8 W8A8</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>11759.473</v>
+        <v>31556.192</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>636.2568</v>
+        <v>1559.9448</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>worker_3 accepted/minimax_tp4_shared_down_proj_m4096/kernel.hip</t>
+          <t>worker_0 accepted/minimax_tp4_qkv_proj_m4096/kernel.hip</t>
         </is>
       </c>
       <c r="M23" s="9" t="n">
-        <v>634.1562</v>
+        <v>1561.9083</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>634.6338</v>
+        <v>1577.3059</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>18.5435</v>
+        <v>20.2036</v>
       </c>
       <c r="P23" s="10" t="n">
-        <v>1754.3497</v>
+        <v>1920.3613</v>
       </c>
       <c r="Q23" s="11" t="inlineStr">
         <is>
@@ -2379,18 +2440,23 @@
         </is>
       </c>
       <c r="S23" s="10" t="n">
-        <v>60.9546</v>
+        <v>74.24509999999999</v>
       </c>
       <c r="T23" s="7" t="inlineStr">
         <is>
           <t>2026-08-23 18:45</t>
+        </is>
+      </c>
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>minimaxm3-dsh-tp8-m4096-1-b0482833</t>
+          <t>minimaxm3-dsh-tp4-m4096-1-0c2f84a9</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2400,22 +2466,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>minimaxM3-dsh-TP8-M4096-1</t>
+          <t>minimaxM3-dsh_TP4_M4096-1</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>qkv_proj</t>
+          <t>qkv_proj_and_indexer_qk</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
         <v>4096</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1280</v>
+        <v>2560</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>6144</v>
@@ -2426,27 +2492,27 @@
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>41000.618</v>
+        <v>35918.768</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>475.5491</v>
+        <v>1081.6037</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>worker_0 accepted/minimax_tp8_qkv_proj_m4096/kernel.hip</t>
+          <t>worker_1 accepted/minimax_tp4_qkv_proj_and_indexer_qk_m4096/kernel.hip</t>
         </is>
       </c>
       <c r="M24" s="4" t="n">
-        <v>474.8046</v>
+        <v>1089.0154</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>475.4174</v>
+        <v>1102.6435</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>86.3526</v>
+        <v>32.9828</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>8535.262199999999</v>
+        <v>3198.2791</v>
       </c>
       <c r="Q24" s="6" t="inlineStr">
         <is>
@@ -2459,18 +2525,23 @@
         </is>
       </c>
       <c r="S24" s="5" t="n">
-        <v>135.6864</v>
+        <v>118.317</v>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29 03:28</t>
+          <t>2026-08-23 18:45</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>minimaxm3-dsh-tp8-m4096-1-b0482833</t>
+          <t>minimaxm3-dsh-tp4-m4096-1-0c2f84a9</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -2480,25 +2551,25 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>minimaxM3-dsh-TP8-M4096-1</t>
+          <t>minimaxM3-dsh_TP4_M4096-1</t>
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>qkv_proj_and_indexer_qk</t>
+          <t>o_proj</t>
         </is>
       </c>
       <c r="F25" s="8" t="n">
         <v>4096</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>1536</v>
+        <v>6144</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>6144</v>
+        <v>2048</v>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
@@ -2506,27 +2577,27 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>35604.698</v>
+        <v>29702.473</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>531.2226000000001</v>
+        <v>765.9098</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>worker_1 accepted/minimax_tp8_qkv_proj_and_indexer_qk_m4096/kernel.hip</t>
+          <t>worker_2 accepted/minimax_tp4_o_proj_m4096/kernel.hip</t>
         </is>
       </c>
       <c r="M25" s="9" t="n">
-        <v>519.4666</v>
+        <v>752.485</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>520.489</v>
+        <v>753.6546</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>68.54089999999999</v>
+        <v>39.4725</v>
       </c>
       <c r="P25" s="10" t="n">
-        <v>6754.0879</v>
+        <v>3847.2513</v>
       </c>
       <c r="Q25" s="11" t="inlineStr">
         <is>
@@ -2539,18 +2610,23 @@
         </is>
       </c>
       <c r="S25" s="10" t="n">
-        <v>148.8246</v>
+        <v>136.9851</v>
       </c>
       <c r="T25" s="7" t="inlineStr">
         <is>
-          <t>2026-08-29 03:28</t>
+          <t>2026-08-23 18:45</t>
+        </is>
+      </c>
+      <c r="U25" s="7" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>minimaxm3-dsh-tp8-m4096-1-b0482833</t>
+          <t>minimaxm3-dsh-tp4-m4096-1-0c2f84a9</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2560,53 +2636,53 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>minimaxM3-dsh-TP8-M4096-1</t>
+          <t>minimaxM3-dsh_TP4_M4096-1</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>o_proj</t>
+          <t>shared_gate_up_proj</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
         <v>4096</v>
       </c>
       <c r="G26" s="3" t="n">
+        <v>1536</v>
+      </c>
+      <c r="H26" s="3" t="n">
         <v>6144</v>
       </c>
-      <c r="H26" s="3" t="n">
-        <v>1024</v>
-      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
           <t>INT8 W8A8</t>
         </is>
       </c>
       <c r="J26" s="4" t="n">
-        <v>19897.517</v>
+        <v>19776.488</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>397.4462</v>
+        <v>986.5248</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>worker_2 accepted/minimax_tp8_o_proj_m4096/kernel.hip</t>
+          <t>worker_3 accepted/minimax_tp4_shared_gate_up_proj_m4096/kernel.hip</t>
         </is>
       </c>
       <c r="M26" s="4" t="n">
-        <v>394.5048</v>
+        <v>962.3475</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>394.9032</v>
+        <v>965.7874</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>50.4367</v>
+        <v>20.5503</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>4943.6688</v>
+        <v>1955.0258</v>
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
@@ -2619,18 +2695,23 @@
         </is>
       </c>
       <c r="S26" s="5" t="n">
-        <v>130.6438</v>
+        <v>80.3342</v>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29 03:28</t>
+          <t>2026-08-23 18:45</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>minimaxm3-dsh-tp8-m4096-1-b0482833</t>
+          <t>minimaxm3-dsh-tp4-m4096-1-0c2f84a9</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -2640,53 +2721,53 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>minimaxM3-dsh-TP8-M4096-1</t>
+          <t>minimaxM3-dsh_TP4_M4096-1</t>
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>shared_gate_up_proj</t>
+          <t>shared_down_proj</t>
         </is>
       </c>
       <c r="F27" s="8" t="n">
         <v>4096</v>
       </c>
       <c r="G27" s="8" t="n">
+        <v>6144</v>
+      </c>
+      <c r="H27" s="8" t="n">
         <v>768</v>
       </c>
-      <c r="H27" s="8" t="n">
-        <v>6144</v>
-      </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
           <t>INT8 W8A8</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>31882.257</v>
+        <v>11759.473</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>319.166</v>
+        <v>636.2568</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>worker_3 accepted/minimax_tp8_shared_gate_up_proj_m4096/kernel.hip</t>
+          <t>worker_3 accepted/minimax_tp4_shared_down_proj_m4096/kernel.hip</t>
         </is>
       </c>
       <c r="M27" s="9" t="n">
-        <v>311.9345</v>
+        <v>634.1562</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>312.3682</v>
+        <v>634.6338</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>102.2082</v>
+        <v>18.5435</v>
       </c>
       <c r="P27" s="10" t="n">
-        <v>10120.8163</v>
+        <v>1754.3497</v>
       </c>
       <c r="Q27" s="11" t="inlineStr">
         <is>
@@ -2699,11 +2780,16 @@
         </is>
       </c>
       <c r="S27" s="10" t="n">
-        <v>123.9193</v>
+        <v>60.9546</v>
       </c>
       <c r="T27" s="7" t="inlineStr">
         <is>
-          <t>2026-08-29 03:28</t>
+          <t>2026-08-23 18:45</t>
+        </is>
+      </c>
+      <c r="U27" s="7" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
         </is>
       </c>
     </row>
@@ -2728,45 +2814,45 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>shared_down_proj</t>
+          <t>qkv_proj</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
         <v>4096</v>
       </c>
       <c r="G28" s="3" t="n">
+        <v>1280</v>
+      </c>
+      <c r="H28" s="3" t="n">
         <v>6144</v>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>384</v>
-      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
           <t>INT8 W8A8</t>
         </is>
       </c>
       <c r="J28" s="4" t="n">
-        <v>22389.162</v>
+        <v>41000.618</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>312.472</v>
+        <v>475.5491</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>worker_3 accepted/minimax_tp8_shared_down_proj_m4096/kernel.hip</t>
+          <t>worker_0 accepted/minimax_tp8_qkv_proj_m4096/kernel.hip</t>
         </is>
       </c>
       <c r="M28" s="4" t="n">
-        <v>311.0093</v>
+        <v>474.8046</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>311.135</v>
+        <v>475.4174</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>71.98869999999999</v>
+        <v>86.3526</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>7098.871</v>
+        <v>8535.262199999999</v>
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
@@ -2779,28 +2865,33 @@
         </is>
       </c>
       <c r="S28" s="5" t="n">
-        <v>62.144</v>
+        <v>135.6864</v>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
           <t>2026-08-29 03:28</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>glm5-2-dsh-tp8-m4096-1-e6a280a2</t>
+          <t>minimaxm3-dsh-tp8-m4096-1-b0482833</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>GLM5.2 (gfx928 INT8 W8A8)</t>
+          <t>MiniMax-M3 (gfx928 INT8 W8A8)</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>glm5.2-dsh-TP8-M4096-1</t>
+          <t>minimaxM3-dsh-TP8-M4096-1</t>
         </is>
       </c>
       <c r="D29" s="8" t="n">
@@ -2808,14 +2899,14 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>fused_qkv_a_proj</t>
+          <t>qkv_proj_and_indexer_qk</t>
         </is>
       </c>
       <c r="F29" s="8" t="n">
         <v>4096</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>2624</v>
+        <v>1536</v>
       </c>
       <c r="H29" s="8" t="n">
         <v>6144</v>
@@ -2826,27 +2917,27 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>68661.417</v>
+        <v>35604.698</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>937.5793</v>
+        <v>531.2226000000001</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>worker_0 accepted/glm_tp8_fused_qkv_a_proj_m4096/kernel.hip</t>
+          <t>worker_1 accepted/minimax_tp8_qkv_proj_and_indexer_qk_m4096/kernel.hip</t>
         </is>
       </c>
       <c r="M29" s="9" t="n">
-        <v>938.0713</v>
+        <v>519.4666</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>939.324</v>
+        <v>520.489</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>73.1942</v>
+        <v>68.54089999999999</v>
       </c>
       <c r="P29" s="10" t="n">
-        <v>7219.4245</v>
+        <v>6754.0879</v>
       </c>
       <c r="Q29" s="11" t="inlineStr">
         <is>
@@ -2859,28 +2950,33 @@
         </is>
       </c>
       <c r="S29" s="10" t="n">
-        <v>140.7891</v>
+        <v>148.8246</v>
       </c>
       <c r="T29" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31 11:23</t>
+          <t>2026-08-29 03:28</t>
+        </is>
+      </c>
+      <c r="U29" s="7" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>glm5-2-dsh-tp8-m4096-1-e6a280a2</t>
+          <t>minimaxm3-dsh-tp8-m4096-1-b0482833</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>GLM5.2 (gfx928 INT8 W8A8)</t>
+          <t>MiniMax-M3 (gfx928 INT8 W8A8)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>glm5.2-dsh-TP8-M4096-1</t>
+          <t>minimaxM3-dsh-TP8-M4096-1</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
@@ -2888,17 +2984,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>q_b_proj</t>
+          <t>o_proj</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
         <v>4096</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>2048</v>
+        <v>6144</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>2048</v>
+        <v>1024</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
@@ -2906,27 +3002,27 @@
         </is>
       </c>
       <c r="J30" s="4" t="n">
-        <v>14385.571</v>
+        <v>19897.517</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>220.1365</v>
+        <v>397.4462</v>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>worker_1 accepted/glm_tp8_q_b_proj_m4096/kernel.hip</t>
+          <t>worker_2 accepted/minimax_tp8_o_proj_m4096/kernel.hip</t>
         </is>
       </c>
       <c r="M30" s="4" t="n">
-        <v>215.4358</v>
+        <v>394.5048</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>215.7486</v>
+        <v>394.9032</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>66.7743</v>
+        <v>50.4367</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>6577.4285</v>
+        <v>4943.6688</v>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
@@ -2939,28 +3035,33 @@
         </is>
       </c>
       <c r="S30" s="5" t="n">
-        <v>159.4895</v>
+        <v>130.6438</v>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31 11:23</t>
+          <t>2026-08-29 03:28</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>glm5-2-dsh-tp8-m4096-1-e6a280a2</t>
+          <t>minimaxm3-dsh-tp8-m4096-1-b0482833</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>GLM5.2 (gfx928 INT8 W8A8)</t>
+          <t>MiniMax-M3 (gfx928 INT8 W8A8)</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>glm5.2-dsh-TP8-M4096-1</t>
+          <t>minimaxM3-dsh-TP8-M4096-1</t>
         </is>
       </c>
       <c r="D31" s="8" t="n">
@@ -2968,17 +3069,17 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>kv_b_proj</t>
+          <t>shared_gate_up_proj</t>
         </is>
       </c>
       <c r="F31" s="8" t="n">
         <v>4096</v>
       </c>
       <c r="G31" s="8" t="n">
-        <v>3584</v>
+        <v>768</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>512</v>
+        <v>6144</v>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
@@ -2986,27 +3087,27 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>6939.939</v>
+        <v>31882.257</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>137.404</v>
+        <v>319.166</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>worker_1 accepted/glm_tp8_kv_b_proj_m4096/kernel.hip</t>
+          <t>worker_3 accepted/minimax_tp8_shared_gate_up_proj_m4096/kernel.hip</t>
         </is>
       </c>
       <c r="M31" s="9" t="n">
-        <v>134.7564</v>
+        <v>311.9345</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>134.9396</v>
+        <v>312.3682</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>51.4999</v>
+        <v>102.2082</v>
       </c>
       <c r="P31" s="10" t="n">
-        <v>5049.9901</v>
+        <v>10120.8163</v>
       </c>
       <c r="Q31" s="11" t="inlineStr">
         <is>
@@ -3019,28 +3120,33 @@
         </is>
       </c>
       <c r="S31" s="10" t="n">
-        <v>111.5523</v>
+        <v>123.9193</v>
       </c>
       <c r="T31" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31 11:23</t>
+          <t>2026-08-29 03:28</t>
+        </is>
+      </c>
+      <c r="U31" s="7" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>glm5-2-dsh-tp8-m4096-1-e6a280a2</t>
+          <t>minimaxm3-dsh-tp8-m4096-1-b0482833</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>GLM5.2 (gfx928 INT8 W8A8)</t>
+          <t>MiniMax-M3 (gfx928 INT8 W8A8)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>glm5.2-dsh-TP8-M4096-1</t>
+          <t>minimaxM3-dsh-TP8-M4096-1</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
@@ -3048,7 +3154,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>o_proj</t>
+          <t>shared_down_proj</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
@@ -3058,7 +3164,7 @@
         <v>6144</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>2048</v>
+        <v>384</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
@@ -3066,27 +3172,27 @@
         </is>
       </c>
       <c r="J32" s="4" t="n">
-        <v>54775.797</v>
+        <v>22389.162</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>759.9215</v>
+        <v>312.472</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>worker_2 accepted/glm_tp8_o_proj_m4096/kernel.hip</t>
+          <t>worker_3 accepted/minimax_tp8_shared_down_proj_m4096/kernel.hip</t>
         </is>
       </c>
       <c r="M32" s="4" t="n">
-        <v>755.8016</v>
+        <v>311.0093</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>756.3576</v>
+        <v>311.135</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>72.4738</v>
+        <v>71.98869999999999</v>
       </c>
       <c r="P32" s="5" t="n">
-        <v>7147.3776</v>
+        <v>7098.871</v>
       </c>
       <c r="Q32" s="6" t="inlineStr">
         <is>
@@ -3099,11 +3205,16 @@
         </is>
       </c>
       <c r="S32" s="5" t="n">
-        <v>136.384</v>
+        <v>62.144</v>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31 11:23</t>
+          <t>2026-08-29 03:28</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
         </is>
       </c>
     </row>
@@ -3128,14 +3239,14 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>shared_gate_up_proj</t>
+          <t>fused_qkv_a_proj</t>
         </is>
       </c>
       <c r="F33" s="8" t="n">
         <v>4096</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>512</v>
+        <v>2624</v>
       </c>
       <c r="H33" s="8" t="n">
         <v>6144</v>
@@ -3146,27 +3257,27 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>21254.589</v>
+        <v>68661.417</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>273.8345</v>
+        <v>937.5793</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>worker_3 accepted/glm_tp8_shared_gate_up_proj_m4096/kernel.hip</t>
+          <t>worker_0 accepted/glm_tp8_fused_qkv_a_proj_m4096/kernel.hip</t>
         </is>
       </c>
       <c r="M33" s="9" t="n">
-        <v>272.711</v>
+        <v>938.0713</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>272.9974</v>
+        <v>939.324</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>77.93810000000001</v>
+        <v>73.1942</v>
       </c>
       <c r="P33" s="10" t="n">
-        <v>7693.8143</v>
+        <v>7219.4245</v>
       </c>
       <c r="Q33" s="11" t="inlineStr">
         <is>
@@ -3179,11 +3290,16 @@
         </is>
       </c>
       <c r="S33" s="10" t="n">
-        <v>94.4949</v>
+        <v>140.7891</v>
       </c>
       <c r="T33" s="7" t="inlineStr">
         <is>
           <t>2026-08-31 11:23</t>
+        </is>
+      </c>
+      <c r="U33" s="7" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
         </is>
       </c>
     </row>
@@ -3208,67 +3324,412 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>shared_down_proj</t>
+          <t>q_b_proj</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
         <v>4096</v>
       </c>
       <c r="G34" s="3" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>2048</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>INT8 W8A8</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>14385.571</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>220.1365</v>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>worker_1 accepted/glm_tp8_q_b_proj_m4096/kernel.hip</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="n">
+        <v>215.4358</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>215.7486</v>
+      </c>
+      <c r="O34" s="4" t="n">
+        <v>66.7743</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>6577.4285</v>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="S34" s="5" t="n">
+        <v>159.4895</v>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:23</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>glm5-2-dsh-tp8-m4096-1-e6a280a2</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>GLM5.2 (gfx928 INT8 W8A8)</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>glm5.2-dsh-TP8-M4096-1</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>kv_b_proj</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>4096</v>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>3584</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>512</v>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>INT8 W8A8</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>6939.939</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>137.404</v>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>worker_1 accepted/glm_tp8_kv_b_proj_m4096/kernel.hip</t>
+        </is>
+      </c>
+      <c r="M35" s="9" t="n">
+        <v>134.7564</v>
+      </c>
+      <c r="N35" s="9" t="n">
+        <v>134.9396</v>
+      </c>
+      <c r="O35" s="9" t="n">
+        <v>51.4999</v>
+      </c>
+      <c r="P35" s="10" t="n">
+        <v>5049.9901</v>
+      </c>
+      <c r="Q35" s="11" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="R35" s="11" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="n">
+        <v>111.5523</v>
+      </c>
+      <c r="T35" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:23</t>
+        </is>
+      </c>
+      <c r="U35" s="7" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>glm5-2-dsh-tp8-m4096-1-e6a280a2</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>GLM5.2 (gfx928 INT8 W8A8)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>glm5.2-dsh-TP8-M4096-1</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>o_proj</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>4096</v>
+      </c>
+      <c r="G36" s="3" t="n">
         <v>6144</v>
       </c>
-      <c r="H34" s="3" t="n">
+      <c r="H36" s="3" t="n">
+        <v>2048</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>INT8 W8A8</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>54775.797</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>759.9215</v>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>worker_2 accepted/glm_tp8_o_proj_m4096/kernel.hip</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="n">
+        <v>755.8016</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>756.3576</v>
+      </c>
+      <c r="O36" s="4" t="n">
+        <v>72.4738</v>
+      </c>
+      <c r="P36" s="5" t="n">
+        <v>7147.3776</v>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="S36" s="5" t="n">
+        <v>136.384</v>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:23</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>glm5-2-dsh-tp8-m4096-1-e6a280a2</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>GLM5.2 (gfx928 INT8 W8A8)</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>glm5.2-dsh-TP8-M4096-1</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>shared_gate_up_proj</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>4096</v>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>512</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>6144</v>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>INT8 W8A8</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>21254.589</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>273.8345</v>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>worker_3 accepted/glm_tp8_shared_gate_up_proj_m4096/kernel.hip</t>
+        </is>
+      </c>
+      <c r="M37" s="9" t="n">
+        <v>272.711</v>
+      </c>
+      <c r="N37" s="9" t="n">
+        <v>272.9974</v>
+      </c>
+      <c r="O37" s="9" t="n">
+        <v>77.93810000000001</v>
+      </c>
+      <c r="P37" s="10" t="n">
+        <v>7693.8143</v>
+      </c>
+      <c r="Q37" s="11" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="R37" s="11" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="n">
+        <v>94.4949</v>
+      </c>
+      <c r="T37" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:23</t>
+        </is>
+      </c>
+      <c r="U37" s="7" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>glm5-2-dsh-tp8-m4096-1-e6a280a2</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>GLM5.2 (gfx928 INT8 W8A8)</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>glm5.2-dsh-TP8-M4096-1</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>shared_down_proj</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>4096</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>6144</v>
+      </c>
+      <c r="H38" s="3" t="n">
         <v>256</v>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>INT8 W8A8</t>
         </is>
       </c>
-      <c r="J34" s="4" t="n">
+      <c r="J38" s="4" t="n">
         <v>17700.262</v>
       </c>
-      <c r="K34" s="4" t="n">
+      <c r="K38" s="4" t="n">
         <v>278.4414</v>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>worker_3 accepted/glm_tp8_shared_down_proj_m4096/kernel.hip</t>
         </is>
       </c>
-      <c r="M34" s="4" t="n">
+      <c r="M38" s="4" t="n">
         <v>273.6263</v>
       </c>
-      <c r="N34" s="4" t="n">
+      <c r="N38" s="4" t="n">
         <v>274.4647</v>
       </c>
-      <c r="O34" s="4" t="n">
+      <c r="O38" s="4" t="n">
         <v>64.68770000000001</v>
       </c>
-      <c r="P34" s="5" t="n">
+      <c r="P38" s="5" t="n">
         <v>6368.7718</v>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="S34" s="5" t="n">
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="S38" s="5" t="n">
         <v>47.0894</v>
       </c>
-      <c r="T34" s="2" t="inlineStr">
+      <c r="T38" s="2" t="inlineStr">
         <is>
           <t>2026-08-31 11:23</t>
         </is>
       </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T34"/>
+  <autoFilter ref="A1:U38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3279,7 +3740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3292,6 +3753,7 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3345,6 +3807,11 @@
           <t>平均提升%</t>
         </is>
       </c>
+      <c r="K1" s="12" t="inlineStr">
+        <is>
+          <t>验收状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
@@ -3363,59 +3830,69 @@
       <c r="D2" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="E2" s="14" t="n">
+      <c r="E2" s="4" t="n">
         <v>67.76134469439091</v>
       </c>
-      <c r="F2" s="14" t="n">
+      <c r="F2" s="4" t="n">
         <v>51.49990132405507</v>
       </c>
-      <c r="G2" s="14" t="n">
+      <c r="G2" s="4" t="n">
         <v>77.93814318275388</v>
       </c>
-      <c r="H2" s="14" t="n">
+      <c r="H2" s="4" t="n">
         <v>431.7337226867676</v>
       </c>
-      <c r="I2" s="14" t="n">
+      <c r="I2" s="4" t="n">
         <v>114.9665361990575</v>
       </c>
-      <c r="J2" s="14" t="n">
+      <c r="J2" s="4" t="n">
         <v>6676.13446943909</v>
       </c>
+      <c r="K2" s="13" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Hy3 (gfx928 INT8 W8A8)</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>hy3-dsh-TP4-m16-2</t>
         </is>
       </c>
-      <c r="C3" s="15" t="n">
+      <c r="C3" s="14" t="n">
         <v>4</v>
       </c>
       <c r="D3" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="9" t="n">
         <v>3.835974172629011</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="9" t="n">
         <v>2.54314615088639</v>
       </c>
-      <c r="G3" s="16" t="n">
+      <c r="G3" s="9" t="n">
         <v>6.397726665631898</v>
       </c>
-      <c r="H3" s="16" t="n">
+      <c r="H3" s="9" t="n">
         <v>15.96528396010399</v>
       </c>
-      <c r="I3" s="16" t="n">
+      <c r="I3" s="9" t="n">
         <v>10.9152606320697</v>
       </c>
-      <c r="J3" s="16" t="n">
+      <c r="J3" s="9" t="n">
         <v>283.5974172629011</v>
+      </c>
+      <c r="K3" s="14" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -3426,7 +3903,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>hy3-dsh-TP8-M4096-1</t>
+          <t>hy3-dsh-TP8-M16-9.8</t>
         </is>
       </c>
       <c r="C4" s="13" t="n">
@@ -3435,131 +3912,151 @@
       <c r="D4" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E4" s="14" t="n">
-        <v>79.60448038261703</v>
-      </c>
-      <c r="F4" s="14" t="n">
-        <v>50.0325901304917</v>
-      </c>
-      <c r="G4" s="14" t="n">
-        <v>144.8833111743286</v>
-      </c>
-      <c r="H4" s="14" t="n">
-        <v>222.1176135540009</v>
-      </c>
-      <c r="I4" s="14" t="n">
-        <v>101.3860739200574</v>
-      </c>
-      <c r="J4" s="14" t="n">
-        <v>7860.448038261703</v>
+      <c r="E4" s="4" t="n">
+        <v>3.527283816288152</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>1.996580472083673</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>5.327286729048045</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>12.87489391863346</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>6.945020444751377</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>252.7283816288152</v>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>仅worker验收(未过最终验收)</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Hy3 (gfx928 INT8 W8A8)</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>hy3_TP4_M4096_dsh-test1</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="n">
-        <v>4</v>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>hy3-dsh-TP8-M4096-1</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>8</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="16" t="n">
-        <v>26.78961929452523</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>20.39344380201025</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <v>31.77520650070368</v>
-      </c>
-      <c r="H5" s="16" t="n">
-        <v>499.0435004234314</v>
-      </c>
-      <c r="I5" s="16" t="n">
-        <v>93.93245897749709</v>
-      </c>
-      <c r="J5" s="16" t="n">
-        <v>2578.961929452524</v>
+      <c r="E5" s="9" t="n">
+        <v>79.60448038261703</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>50.0325901304917</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>144.8833111743286</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>222.1176135540009</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>101.3860739200574</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>7860.448038261703</v>
+      </c>
+      <c r="K5" s="14" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
+          <t>Hy3 (gfx928 INT8 W8A8)</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>hy3_TP4_M4096_dsh-test1</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>26.78961929452523</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>20.39344380201025</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>31.77520650070368</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>499.0435004234314</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>93.93245897749709</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>2578.961929452524</v>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
           <t>MiniMax-M3 (gfx928 INT8 W8A8)</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>minimax-dsh-TP8-m16-1</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>3.586128257177933</v>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>2.478421379962978</v>
-      </c>
-      <c r="G6" s="14" t="n">
-        <v>6.035223999381635</v>
-      </c>
-      <c r="H6" s="14" t="n">
-        <v>22.27343809604645</v>
-      </c>
-      <c r="I6" s="14" t="n">
-        <v>9.816314079097454</v>
-      </c>
-      <c r="J6" s="14" t="n">
-        <v>258.6128257177933</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>MiniMax-M3 (gfx928 INT8 W8A8)</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>minimaxM3-dsh-TP8-M4096-1</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="14" t="n">
         <v>8</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="16" t="n">
-        <v>75.90541223509794</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>50.43668752426038</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>102.2081627804804</v>
-      </c>
-      <c r="H7" s="16" t="n">
-        <v>402.3439788818359</v>
-      </c>
-      <c r="I7" s="16" t="n">
-        <v>120.2436030001635</v>
-      </c>
-      <c r="J7" s="16" t="n">
-        <v>7490.541223509796</v>
+      <c r="E7" s="9" t="n">
+        <v>3.586128257177933</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>2.478421379962978</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>6.035223999381635</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>22.27343809604645</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>9.816314079097454</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>258.6128257177933</v>
+      </c>
+      <c r="K7" s="14" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -3570,36 +4067,82 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>minimaxM3-dsh_TP4_M4096-1</t>
+          <t>minimaxM3-dsh-TP8-M4096-1</t>
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="4" t="n">
+        <v>75.90541223509794</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>50.43668752426038</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>102.2081627804804</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>402.3439788818359</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>120.2436030001635</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>7490.541223509796</v>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>MiniMax-M3 (gfx928 INT8 W8A8)</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>minimaxM3-dsh_TP4_M4096-1</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>26.35053437676494</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F9" s="9" t="n">
         <v>18.54349694652441</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G9" s="9" t="n">
         <v>39.47251331324</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="H9" s="9" t="n">
         <v>999.9824714660645</v>
       </c>
-      <c r="I8" s="14" t="n">
+      <c r="I9" s="9" t="n">
         <v>94.16719280919206</v>
       </c>
-      <c r="J8" s="14" t="n">
+      <c r="J9" s="9" t="n">
         <v>2535.053437676494</v>
       </c>
+      <c r="K9" s="14" t="inlineStr">
+        <is>
+          <t>最终验收通过</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J8"/>
+  <autoFilter ref="A1:K9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3678,7 +4221,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>kv_b_proj</t>
         </is>
@@ -3695,7 +4238,7 @@
       <c r="E3" s="9" t="n">
         <v>111.55233090221</v>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t>glm5.2-dsh-TP8-M4096-1/TP8/M4096</t>
         </is>
@@ -3708,25 +4251,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>34.84875561528084</v>
+        <v>30.85639973287952</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>72.47377554571302</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>92.18942029297098</v>
+        <v>82.18486913359196</v>
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>glm5.2-dsh-TP8-M4096-1/TP8/M4096, hy3-dsh-TP4-m16-2/TP4/M16, hy3-dsh-TP8-M4096-1/TP8/M4096, hy3_TP4_M4096_dsh-test1/TP4/M4096, minimax-dsh-TP8-m16-1/TP8/M16, minimaxM3-dsh-TP8-M4096-1/TP8/M4096, minimaxM3-dsh_TP4_M4096-1/TP4/M4096</t>
+          <t>glm5.2-dsh-TP8-M4096-1/TP8/M4096, hy3-dsh-TP4-m16-2/TP4/M16, hy3-dsh-TP8-M16-9.8/TP8/M16, hy3-dsh-TP8-M4096-1/TP8/M4096, hy3_TP4_M4096_dsh-test1/TP4/M4096, minimax-dsh-TP8-m16-1/TP8/M16, minimaxM3-dsh-TP8-M4096-1/TP8/M4096, minimaxM3-dsh_TP4_M4096-1/TP4/M4096</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>q_b_proj</t>
         </is>
@@ -3743,7 +4286,7 @@
       <c r="E5" s="9" t="n">
         <v>159.4894618299889</v>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>glm5.2-dsh-TP8-M4096-1/TP8/M4096</t>
         </is>
@@ -3756,25 +4299,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>34.23538697872744</v>
+        <v>29.89824019718791</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>86.35262163311907</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>79.66643329949282</v>
+        <v>69.52755767323966</v>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>hy3-dsh-TP4-m16-2/TP4/M16, hy3-dsh-TP8-M4096-1/TP8/M4096, hy3_TP4_M4096_dsh-test1/TP4/M4096, minimax-dsh-TP8-m16-1/TP8/M16, minimaxM3-dsh-TP8-M4096-1/TP8/M4096, minimaxM3-dsh_TP4_M4096-1/TP4/M4096</t>
+          <t>hy3-dsh-TP4-m16-2/TP4/M16, hy3-dsh-TP8-M16-9.8/TP8/M16, hy3-dsh-TP8-M4096-1/TP8/M4096, hy3_TP4_M4096_dsh-test1/TP4/M4096, minimax-dsh-TP8-m16-1/TP8/M16, minimaxM3-dsh-TP8-M4096-1/TP8/M4096, minimaxM3-dsh_TP4_M4096-1/TP4/M4096</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>qkv_proj_and_indexer_qk</t>
         </is>
@@ -3791,7 +4334,7 @@
       <c r="E7" s="9" t="n">
         <v>91.58040212918337</v>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>minimax-dsh-TP8-m16-1/TP8/M16, minimaxM3-dsh-TP8-M4096-1/TP8/M4096, minimaxM3-dsh_TP4_M4096-1/TP4/M4096</t>
         </is>
@@ -3804,44 +4347,44 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>34.75382001055991</v>
+        <v>30.65916506825038</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>71.98871034823276</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>40.17934567846852</v>
+        <v>35.5197220097463</v>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>glm5.2-dsh-TP8-M4096-1/TP8/M4096, hy3-dsh-TP4-m16-2/TP4/M16, hy3-dsh-TP8-M4096-1/TP8/M4096, hy3_TP4_M4096_dsh-test1/TP4/M4096, minimax-dsh-TP8-m16-1/TP8/M16, minimaxM3-dsh-TP8-M4096-1/TP8/M4096, minimaxM3-dsh_TP4_M4096-1/TP4/M4096</t>
+          <t>glm5.2-dsh-TP8-M4096-1/TP8/M4096, hy3-dsh-TP4-m16-2/TP4/M16, hy3-dsh-TP8-M16-9.8/TP8/M16, hy3-dsh-TP8-M4096-1/TP8/M4096, hy3_TP4_M4096_dsh-test1/TP4/M4096, minimax-dsh-TP8-m16-1/TP8/M16, minimaxM3-dsh-TP8-M4096-1/TP8/M4096, minimaxM3-dsh_TP4_M4096-1/TP4/M4096</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>shared_gate_up_proj</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>55.46724609548004</v>
+        <v>49.19975117467605</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>144.8833111743286</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>77.81683434039668</v>
-      </c>
-      <c r="F9" s="15" t="inlineStr">
-        <is>
-          <t>glm5.2-dsh-TP8-M4096-1/TP8/M4096, hy3-dsh-TP4-m16-2/TP4/M16, hy3-dsh-TP8-M4096-1/TP8/M4096, hy3_TP4_M4096_dsh-test1/TP4/M4096, minimax-dsh-TP8-m16-1/TP8/M16, minimaxM3-dsh-TP8-M4096-1/TP8/M4096, minimaxM3-dsh_TP4_M4096-1/TP4/M4096</t>
+        <v>68.59353136242899</v>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>glm5.2-dsh-TP8-M4096-1/TP8/M4096, hy3-dsh-TP4-m16-2/TP4/M16, hy3-dsh-TP8-M16-9.8/TP8/M16, hy3-dsh-TP8-M4096-1/TP8/M4096, hy3_TP4_M4096_dsh-test1/TP4/M4096, minimax-dsh-TP8-m16-1/TP8/M16, minimaxM3-dsh-TP8-M4096-1/TP8/M4096, minimaxM3-dsh_TP4_M4096-1/TP4/M4096</t>
         </is>
       </c>
     </row>
@@ -3856,7 +4399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3939,33 +4482,33 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>hy3-dsh-tp4-m16-2-368c654c</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Hy3 (gfx928 INT8 W8A8)</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>hy3-dsh-TP4-m16-2</t>
         </is>
       </c>
-      <c r="D3" s="15" t="n">
+      <c r="D3" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="E3" s="15" t="n">
+      <c r="E3" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t>2026-08-26 14:59</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>success(final_report)</t>
         </is>
@@ -3974,7 +4517,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>hy3-dsh-tp8-m4096-1-0ebb994d</t>
+          <t>hy3-dsh-tp8-m16-9-8-0161e718</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -3984,7 +4527,7 @@
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>hy3-dsh-TP8-M4096-1</t>
+          <t>hy3-dsh-TP8-M16-9.8</t>
         </is>
       </c>
       <c r="D4" s="13" t="n">
@@ -3993,45 +4536,41 @@
       <c r="E4" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr"/>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>success(final_report)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>hy3-dsh-tp8-m4096-1-0ebb994d</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Hy3 (gfx928 INT8 W8A8)</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>hy3-dsh-TP8-M4096-1</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>2026-08-27 07:23</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>success(final_report)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>hy3-tp4-m4096-dsh-test1-bfdf3002</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>Hy3 (gfx928 INT8 W8A8)</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>hy3_TP4_M4096_dsh-test1</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="15" t="inlineStr">
-        <is>
-          <t>2026-08-22 05:44</t>
-        </is>
-      </c>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>success(final_report)</t>
         </is>
@@ -4040,64 +4579,64 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
+          <t>hy3-tp4-m4096-dsh-test1-bfdf3002</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Hy3 (gfx928 INT8 W8A8)</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>hy3_TP4_M4096_dsh-test1</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-22 05:44</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>success(final_report)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
           <t>minimax-dsh-tp8-m16-1-78402260</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>MiniMax-M3 (gfx928 INT8 W8A8)</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>minimax-dsh-TP8-m16-1</t>
         </is>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D7" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E7" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>2026-08-28 17:17</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>success(final_report)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>minimaxm3-dsh-tp4-m4096-1-0c2f84a9</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>MiniMax-M3 (gfx928 INT8 W8A8)</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>minimaxM3-dsh_TP4_M4096-1</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>2026-08-23 18:45</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>success(final_report)</t>
         </is>
@@ -4106,7 +4645,7 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>minimaxm3-dsh-tp8-m4096-1-b0482833</t>
+          <t>minimaxm3-dsh-tp4-m4096-1-0c2f84a9</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
@@ -4116,21 +4655,54 @@
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>minimaxM3-dsh-TP8-M4096-1</t>
+          <t>minimaxM3-dsh_TP4_M4096-1</t>
         </is>
       </c>
       <c r="D8" s="13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E8" s="13" t="n">
         <v>5</v>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
+          <t>2026-08-23 18:45</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>success(final_report)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>minimaxm3-dsh-tp8-m4096-1-b0482833</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>MiniMax-M3 (gfx928 INT8 W8A8)</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>minimaxM3-dsh-TP8-M4096-1</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
           <t>2026-08-29 03:28</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>success(final_report)</t>
         </is>
@@ -4147,7 +4719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4156,148 +4728,174 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>本表汇总 dcu_kernel_auto_opt 任务下所有已完成并通过最终串行验收(status=success, final_report.json)的真实优化任务，</t>
         </is>
       </c>
-      <c r="C1" s="18" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>取每个 (模型×TP×算子×M) 最优已验收 variant 的最终性能；每个 shape 一行。</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>硬件/算子</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>worker29, 4×K500SM_AI / gfx928 (Hygon DCU, CDNA 系); 算子 = INT8 W8A8 GEMM (HIP C++, DUMMA Tensor Core), dtype int8 × fp32 scale → bf16 out</t>
         </is>
       </c>
-      <c r="C2" s="18" t="n"/>
+      <c r="C2" s="16" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Triton基线(µs)</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>固定 Triton Graph 基线中位延迟（fixed table / 实测 graph replay），与 custom 同协议（GPU event、warmup、graph replay median）</t>
         </is>
       </c>
-      <c r="C3" s="18" t="n"/>
+      <c r="C3" s="16" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>探索期Worker最优(µs)</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>并行探索阶段各 worker 在验收轮记录到的最快 median（accepted 轮）。部分行略快于最终验收值，属重测协议差异(最终门限 ≤1.05×worker best)</t>
         </is>
       </c>
-      <c r="C4" s="18" t="n"/>
+      <c r="C4" s="16" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>最终验收最优variant(µs)</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>串行最终验收重新测量并全部 shape 通过(正确性+性能门)的 median —— 本表采用的“最优 variant 性能”主列</t>
         </is>
       </c>
-      <c r="C5" s="18" t="n"/>
+      <c r="C5" s="16" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>加速比(×)</t>
         </is>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="16">
         <f> Triton基线 / 最终验收median</f>
         <v/>
       </c>
-      <c r="C6" s="18" t="n"/>
+      <c r="C6" s="16" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>提升(%)</t>
         </is>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="16">
         <f> (Triton基线/最终验收median − 1) × 100%；任务门槛 minimum_improvement_percent=3.0%（对 plan shape 的最终验收 vs 固定基线）</f>
         <v/>
       </c>
-      <c r="C7" s="18" t="n"/>
+      <c r="C7" s="16" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>计算性能(TOPS)</t>
         </is>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="16">
         <f> 2×M×N×K / final_us，纯算法逻辑 INT8 运算速率（非实测带宽）</f>
         <v/>
       </c>
-      <c r="C8" s="18" t="n"/>
+      <c r="C8" s="16" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>达标/正确性</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>target_met: 最终验收 ≥3% 提升门槛；passed: 最终串行验证正确性通过(CPU int64 exact reference)</t>
         </is>
       </c>
-      <c r="C9" s="18" t="n"/>
+      <c r="C9" s="16" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>验收状态</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>'最终验收通过' = 该任务串行最终验收全部 shape 通过并写出 final_report.json (status=success)；'仅worker验收(未过最终验收)' = 该任务未产出成功 final_report，本行取的是 worker 并行探索阶段已验收最优 variant 的 median（未经最终门限确认）</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>覆盖</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>Hy3: TP4 M16/M4096, TP8 M4096; MiniMax-M3: TP4 M4096, TP8 M16/M4096; GLM5.2: TP8 M4096 —— 共 33 个优化 shape，全部为各任务自身 plan 的优化算子（不含默认42-shape回归项）</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Hy3: TP4 M16/M4096, TP8 M4096 (+TP8 M16 见下条); MiniMax-M3: TP4 M4096, TP8 M16/M4096; GLM5.2: TP8 M4096 —— 共 37 个优化 shape 行，其中 33 行为各任务自身 plan 的最终验收通过算子，4 行为 Hy3 TP8 M16（仅 worker 验收，见下条）；不含默认 42-shape 回归项</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Hy3 TP8 M16 (9.8 任务)</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>任务 hy3-dsh-tp8-m16-9-8-0161e718 的 4 个 M=16 shape 目前无成功 final_report：2026-09-09 07:04 最终验收因性能门限失败（o_proj final 11.745 vs worker best 11.044 &gt; 1.05×）。2026-09-10 重跑验收：qkv_proj ✅、o_proj ✅（首测 11.706 超限，第 1 次重测通过）、shared_gate_up_proj 首测 13.1295 vs 门限 13.112（超 0.13%）时按用户要求暂停，shared_down_proj 未测。本表该 4 行数值取 worker 探索期已验收最优 median</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>生成时间</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>2026-09（数据截至各任务 final_report.json 快照）</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n"/>
+      <c r="C13" s="16" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
